--- a/docs/EEG_kit_BOM_for_bidders_RevC.xlsx
+++ b/docs/EEG_kit_BOM_for_bidders_RevC.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kit BOM" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carrier sub-BOM (generated)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Kit BOM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Carrier sub-BOM (generated)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Read me" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>OPEN: the candidate module presents USB-B and E-24 asks for USB-C. Interim answer is the WH-09 panel pigtail</t>
+          <t>OPEN, and NOT closed by the interim answer. The candidate module presents USB-B and E-24 asks for USB-C; the WH-09 panel pigtail is the interim answer and E-24 says of it, in terms, 'it is not a settled design'. WHAT IS MISSING is an ADuM4160-class isolator module with a USB-C host connector, qualified against E-24 and the DSN-EEG-003 section 3.3 isolation keep-out. Until one exists the non-conformance is live and is carried, not resolved. Bidders who know of such a module should say so</t>
         </is>
       </c>
       <c r="M6" s="4" t="n"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>OPEN: the MAX9814 named in v1 is an AGC part and E-14 requires AGC off. Mounts on MP-01 at J21; the boom carries the bare capsule</t>
+          <t>OPEN, but narrower than it was. The AGC CONFLICT IS RESOLVED: the MAX9814 of package v1 is an AGC part, is NOT APPROVED, and is superseded here -- E-14 requires AGC off, and the fixed-gain MAX4466 class named here is E-14's own preferred route. What is still open is the SELECTION, not the conflict -- E-14 reads 'which preamplifier is not settled' and specifies the module BY INTERFACE in ICD-EEG-006 section 2.9 until one is bought and measured. Quote against the interface. Mounts on MP-01 at J21; the boom carries the bare capsule</t>
         </is>
       </c>
       <c r="M12" s="4" t="n"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>OPEN: no module is known to meet E-15's hardware mute. Fallback is a capsule with a TS5A3159 analogue switch on an adapter</t>
+          <t>OPEN, and the only row in this BOM with NO PART AT ALL. E-15 requires the audio path to be hardware-gatable on MIC_MUTE (GPIO21); a catalogue search found no breakout with a mute pin -- the common electret and MEMS boards (SparkFun, Pololu, Adafruit 1063, INMP441) bring out audio and power only. The fallback is a capsule plus a TS5A3159 analogue switch on a programme-designed adapter, which is a NEW DRAWING and has not been drawn. Thirteen module assemblies per unit and this is the unspecified one. Bidders: quote the other twelve and say whether you would build the adapter to a drawing when one exists</t>
         </is>
       </c>
       <c r="M13" s="4" t="n"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>v1 specified two layers and 130 x 124 mm; see DSN-EEG-003 Rev C section 3</t>
+          <t>v1 specified two layers and 130 x 124 mm; see DSN-EEG-003 Rev D section 3</t>
         </is>
       </c>
       <c r="M17" s="4" t="n"/>
@@ -3210,11 +3210,11 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>C1 C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16</t>
+          <t>C1 C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C21 C41 C61</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>C21 C41 C61</t>
+          <t>C22 C42 C62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>100n X7R 25V +/-15% over range</t>
+          <t>22n C0G 50V</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Murata GCM188R71E104KA57D</t>
+          <t>Murata GCM1885C1H223JA16D</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Sallen-Key C to AGND_REF, channel 1. A 100 nF C0G is not stocked in 0603, so this is X7R and the filter corner tolerance in TST-EEG-004 allows for it.</t>
+          <t>Sallen-Key feedback C, sets Q = 0.74, channel 1.  C0G for the same reason as C21; the ratio 22/10 is what holds Q at 0.742.</t>
         </is>
       </c>
       <c r="I5" s="4" t="n"/>
@@ -3327,16 +3327,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>C22 C42 C62</t>
+          <t>C23 C24 C43 C44 C50 C51 C52 C63 C64 C80 C81 C82 C83 C84 C85 C86 C87 C88</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>220n X7R 25V</t>
+          <t>100n X7R 25V</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Murata GCM188R71E224KA64D</t>
+          <t>Murata GCM188R71E104KA57D</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Sallen-Key feedback C, sets Q = 0.74, channel 1</t>
+          <t>AVDD decoupling at U1</t>
         </is>
       </c>
       <c r="I6" s="4" t="n"/>
@@ -3366,16 +3366,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>C23 C24 C43 C44 C50 C51 C52 C63 C64 C80 C81 C82 C83 C84 C85 C86 C87 C88</t>
+          <t>C102 C103</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>100n X7R 25V</t>
+          <t>100n X7R 50V</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Murata GCM188R71E104KA57D</t>
+          <t>Murata GCM188R71H104KA57D</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>AVDD decoupling at U1</t>
+          <t>AVDD high-frequency decoupling</t>
         </is>
       </c>
       <c r="I7" s="4" t="n"/>
@@ -3405,26 +3405,26 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>C102 C103</t>
+          <t>D1 D2 D3 D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D23</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>100n X7R 50V</t>
+          <t>BAV99</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Murata GCM188R71H104KA57D</t>
+          <t>Nexperia BAV99,215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>AVDD high-frequency decoupling</t>
+          <t>clamp to AVDD/AVSS, Fz scalp</t>
         </is>
       </c>
       <c r="I8" s="4" t="n"/>
@@ -3444,16 +3444,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>D1 D2 D3 D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D23</t>
+          <t>D20 D40 D60</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>BAV99</t>
+          <t>BAT54S</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Nexperia BAV99,215</t>
+          <t>Nexperia BAT54S,215</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>clamp to AVDD/AVSS, Fz scalp</t>
+          <t>precision-rectifier Schottky pair (pin 3 at the op-amp output), channel 1</t>
         </is>
       </c>
       <c r="I9" s="4" t="n"/>
@@ -3483,16 +3483,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>D20 D40 D60</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>BAT54S</t>
+          <t>PESD5V0S2BT</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Nexperia BAT54S,215</t>
+          <t>Nexperia PESD5V0S2BT,215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>precision-rectifier Schottky pair (pin 3 at the op-amp output), channel 1</t>
+          <t>transient suppressor on the charge input</t>
         </is>
       </c>
       <c r="I10" s="4" t="n"/>
@@ -3522,26 +3522,26 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>FID1 FID2 FID3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>PESD5V0S2BT</t>
+          <t>global fiducial</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>Fiducial_1mm_Mask3mm</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Nexperia PESD5V0S2BT,215</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>transient suppressor on the charge input</t>
+          <t>1 mm copper, 3 mm mask opening, no net</t>
         </is>
       </c>
       <c r="I11" s="4" t="n"/>
@@ -3561,26 +3561,26 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FID1 FID2 FID3</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>global fiducial</t>
+          <t>PTC 1.1 A hold / 2.2 A trip</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Fiducial_1mm_Mask3mm</t>
+          <t>R_1206_3216Metric</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bourns MF-MSMF110-2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>1 mm copper, 3 mm mask opening, no net</t>
+          <t>resettable fuse in the charge input</t>
         </is>
       </c>
       <c r="I12" s="4" t="n"/>
@@ -3604,22 +3604,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>PTC 1.1 A hold / 2.2 A trip</t>
+          <t>ADS1299 module #1 digital</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>R_1206_3216Metric</t>
+          <t>PinSocket_1x12_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Bourns MF-MSMF110-2</t>
+          <t>Samtec SSW-112-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>resettable fuse in the charge input</t>
+          <t>1x12 socket: SPI, control lines, shared clock, 3V3 and 5 V feed to module #1</t>
         </is>
       </c>
       <c r="I13" s="4" t="n"/>
@@ -3643,22 +3643,22 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ADS1299 module #1 digital</t>
+          <t>ADS1299 module #1 analogue signals</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x12_P2.54mm_Vertical</t>
+          <t>PinSocket_1x10_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-112-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-110-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>1x12 socket: SPI, control lines, shared clock, 3V3 and 5 V feed to module #1</t>
+          <t>1x10 socket: eight EEG inputs, the SRB1 reference and the bias drive</t>
         </is>
       </c>
       <c r="I14" s="4" t="n"/>
@@ -3682,22 +3682,22 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ADS1299 module #1 analogue signals</t>
+          <t>ADS1299 module #2 digital</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x10_P2.54mm_Vertical</t>
+          <t>PinSocket_1x12_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-110-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-112-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>1x10 socket: eight EEG inputs, the SRB1 reference and the bias drive</t>
+          <t>1x12 socket: SPI, control lines, shared clock, 3V3 and 5 V feed to module #2</t>
         </is>
       </c>
       <c r="I15" s="4" t="n"/>
@@ -3721,22 +3721,22 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ADS1299 module #2 digital</t>
+          <t>ADS1299 module #2 analogue signals</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x12_P2.54mm_Vertical</t>
+          <t>PinSocket_1x10_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-112-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-110-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>1x12 socket: SPI, control lines, shared clock, 3V3 and 5 V feed to module #2</t>
+          <t>1x10 socket: three EMG inputs, three envelope channels, two spares, SRB1</t>
         </is>
       </c>
       <c r="I16" s="4" t="n"/>
@@ -3760,22 +3760,22 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ADS1299 module #2 analogue signals</t>
+          <t>ADS #1 DAISY_IN / CLKOUT stub</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x10_P2.54mm_Vertical</t>
+          <t>PinSocket_1x04_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-110-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-104-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>1x10 socket: three EMG inputs, three envelope channels, two spares, SRB1</t>
+          <t>1x4 stub: module #2 DOUT into module #1 DAISY_IN and the shared 2.048 MHz clock</t>
         </is>
       </c>
       <c r="I17" s="4" t="n"/>
@@ -3799,22 +3799,22 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ADS #1 DAISY_IN / CLKOUT stub</t>
+          <t>ESP32-S3-DevKitC-1 row A</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x04_P2.54mm_Vertical</t>
+          <t>PinSocket_1x22_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-104-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-122-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>1x4 stub: module #2 DOUT into module #1 DAISY_IN and the shared 2.048 MHz clock</t>
+          <t>1x22 socket, DevKitC-1 left header. Row spacing to J7 is 22.86 mm (0.900 in).</t>
         </is>
       </c>
       <c r="I18" s="4" t="n"/>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ESP32-S3-DevKitC-1 row A</t>
+          <t>ESP32-S3-DevKitC-1 row B</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>1x22 socket, DevKitC-1 left header. Row spacing to J7 is 22.86 mm (0.900 in).</t>
+          <t>1x22 socket, DevKitC-1 right header</t>
         </is>
       </c>
       <c r="I19" s="4" t="n"/>
@@ -3877,22 +3877,22 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>J7</t>
+          <t>J8</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ESP32-S3-DevKitC-1 row B</t>
+          <t>ES8388 codec module</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x22_P2.54mm_Vertical</t>
+          <t>PinSocket_1x14_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-122-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-114-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>1x22 socket, DevKitC-1 right header</t>
+          <t>1x14: I2S, I2C, headphone amplifier output, the stimulus envelope tap and 5 V</t>
         </is>
       </c>
       <c r="I20" s="4" t="n"/>
@@ -3916,22 +3916,22 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>J8</t>
+          <t>J9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ES8388 codec module</t>
+          <t>Codec microphone feeds</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x14_P2.54mm_Vertical</t>
+          <t>PinSocket_1x04_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-114-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-104-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>1x14: I2S, I2C, headphone amplifier output, the stimulus envelope tap and 5 V</t>
+          <t>1x4: voice and room preamp outputs into the codec ADC, and the room-mic mute line</t>
         </is>
       </c>
       <c r="I21" s="4" t="n"/>
@@ -3955,12 +3955,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>J9</t>
+          <t>J10</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Codec microphone feeds</t>
+          <t>ADuM4160 USB isolator, device side</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>1x4: voice and room preamp outputs into the codec ADC, and the room-mic mute line</t>
+          <t>1x4: isolated USB D+/D-, isolated 3V3 and DGND. No carrier copper crosses the barrier. The module's host receptacle is USB-B on the qualified part, not USB-C; WH-09 adapts it. See RUL-EEG-021 section B.</t>
         </is>
       </c>
       <c r="I22" s="4" t="n"/>
@@ -3994,12 +3994,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>J10</t>
+          <t>J11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ADuM4160 USB isolator, device side</t>
+          <t>ATECC608B breakout</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>1x4: isolated USB D+/D-, isolated 3V3 and DGND. No carrier copper crosses the barrier. The module's host receptacle is USB-B on the qualified part, not USB-C; WH-09 adapts it. See RUL-EEG-021 section B.</t>
+          <t>1x4: secure element on the shared I2C bus</t>
         </is>
       </c>
       <c r="I23" s="4" t="n"/>
@@ -4033,22 +4033,22 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>J11</t>
+          <t>J12</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ATECC608B breakout</t>
+          <t>Charger + fuel gauge module</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x04_P2.54mm_Vertical</t>
+          <t>PinSocket_1x08_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-104-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-108-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>1x4: secure element on the shared I2C bus</t>
+          <t>1x8: bq24074-class charger with power path, and the MAX17048 gauge on I2C</t>
         </is>
       </c>
       <c r="I24" s="4" t="n"/>
@@ -4072,22 +4072,22 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>J12</t>
+          <t>J13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Charger + fuel gauge module</t>
+          <t>18650 protected cell</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x08_P2.54mm_Vertical</t>
+          <t>JST_PH_B2B-PH-K_1x02_P2.00mm_Vertical</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-108-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>JST B2B-PH-K-S(LF)(SN)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>1x8: bq24074-class charger with power path, and the MAX17048 gauge on I2C</t>
+          <t>battery input from the keyed cell carrier</t>
         </is>
       </c>
       <c r="I25" s="4" t="n"/>
@@ -4111,22 +4111,22 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>J13</t>
+          <t>J14</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>18650 protected cell</t>
+          <t>Helmet harness -- electrodes (12-way screened)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>JST_PH_B2B-PH-K_1x02_P2.00mm_Vertical</t>
+          <t>PinSocket_1x12_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>JST B2B-PH-K-S(LF)(SN)</t>
+          <t>Samtec SSW-112-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>battery input from the keyed cell carrier</t>
+          <t>1x12 socket: eight scalp electrodes, two ear references, the bias lead and the cable screen.  Nothing digital enters this connector.</t>
         </is>
       </c>
       <c r="I26" s="4" t="n"/>
@@ -4150,22 +4150,22 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>J14</t>
+          <t>J15</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Helmet harness -- electrodes (12-way screened)</t>
+          <t>DIN 42802 EMG1 cheek</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x12_P2.54mm_Vertical</t>
+          <t>DIN42802_1p5mm_Socket</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-112-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Staubli SLB1,5-F / LB-I1,5</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>1x12 socket: eight scalp electrodes, two ear references, the bias lead and the cable screen.  Nothing digital enters this connector.</t>
+          <t>touch-proof 1.5 mm safety socket, EMG1 cheek, colour-coded</t>
         </is>
       </c>
       <c r="I27" s="4" t="n"/>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>J15</t>
+          <t>J16</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DIN 42802 EMG1 cheek</t>
+          <t>DIN 42802 EMG2 submental</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>touch-proof 1.5 mm safety socket, EMG1 cheek, colour-coded</t>
+          <t>touch-proof 1.5 mm safety socket, EMG2 submental, colour-coded</t>
         </is>
       </c>
       <c r="I28" s="4" t="n"/>
@@ -4228,12 +4228,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>J16</t>
+          <t>J17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DIN 42802 EMG2 submental</t>
+          <t>DIN 42802 EMG3 laryngeal</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>touch-proof 1.5 mm safety socket, EMG2 submental, colour-coded</t>
+          <t>touch-proof 1.5 mm safety socket, EMG3 laryngeal, colour-coded</t>
         </is>
       </c>
       <c r="I29" s="4" t="n"/>
@@ -4267,22 +4267,22 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>J17</t>
+          <t>J18</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DIN 42802 EMG3 laryngeal</t>
+          <t>Boom microphone pigtail (TRRS)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>DIN42802_1p5mm_Socket</t>
+          <t>PinSocket_1x04_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Staubli SLB1,5-F / LB-I1,5</t>
+          <t>Samtec SSW-104-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>touch-proof 1.5 mm safety socket, EMG3 laryngeal, colour-coded</t>
+          <t>1x4: to the panel TRRS jack at the left temple</t>
         </is>
       </c>
       <c r="I30" s="4" t="n"/>
@@ -4306,22 +4306,22 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>J18</t>
+          <t>J19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Boom microphone pigtail (TRRS)</t>
+          <t>74HC595 contact-light driver</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x04_P2.54mm_Vertical</t>
+          <t>PinSocket_1x16_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-104-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-116-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>1x4: to the panel TRRS jack at the left temple</t>
+          <t>1x16: shift-register module. Q0..Q7 drive the eight helmet contact lights.</t>
         </is>
       </c>
       <c r="I31" s="4" t="n"/>
@@ -4345,22 +4345,22 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>J19</t>
+          <t>J20</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>74HC595 contact-light driver</t>
+          <t>microSD breakout, SDMMC 1-bit</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x16_P2.54mm_Vertical</t>
+          <t>PinSocket_1x08_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-116-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-108-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>1x16: shift-register module. Q0..Q7 drive the eight helmet contact lights.</t>
+          <t>1x8: microSD card breakout wired for one-bit SDMMC (70 kB/s needed, 2 MB/s available)</t>
         </is>
       </c>
       <c r="I32" s="4" t="n"/>
@@ -4384,22 +4384,22 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>J20</t>
+          <t>J21</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>microSD breakout, SDMMC 1-bit</t>
+          <t>Boom-mic preamp module (part not settled, E-14)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x08_P2.54mm_Vertical</t>
+          <t>PinSocket_1x06_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-108-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-106-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>1x8: microSD card breakout wired for one-bit SDMMC (70 kB/s needed, 2 MB/s available)</t>
+          <t>1x6: fixed-gain boom microphone preamp module. RFQ E-14 forbids automatic gain control, so the MAX9814 of package v1 is NOT APPROVED (AVL-EEG-017); a MAX4466-class fixed-gain board is the reference. The part is an open item and this socket is specified by its interface, not by a chosen module.</t>
         </is>
       </c>
       <c r="I33" s="4" t="n"/>
@@ -4423,22 +4423,22 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>J21</t>
+          <t>J22</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Boom-mic preamp module (part not settled, E-14)</t>
+          <t>EOG / spare electrode header</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x06_P2.54mm_Vertical</t>
+          <t>PinSocket_1x03_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-106-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-103-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>1x6: fixed-gain boom microphone preamp module. RFQ E-14 forbids automatic gain control, so the MAX9814 of package v1 is NOT APPROVED (AVL-EEG-017); a MAX4466-class fixed-gain board is the reference. The part is an open item and this socket is specified by its interface, not by a chosen module.</t>
+          <t>1x3 socket: two spare protected electrode channels and their screen. Wired to panel DIN sockets only when the EOG option is used (RFQ 3.1).</t>
         </is>
       </c>
       <c r="I34" s="4" t="n"/>
@@ -4462,22 +4462,22 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>J22</t>
+          <t>J23</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>EOG / spare electrode header</t>
+          <t>ADS1299 module #1 analogue rails</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x03_P2.54mm_Vertical</t>
+          <t>PinSocket_1x06_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-103-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-106-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>1x3 socket: two spare protected electrode channels and their screen. Wired to panel DIN sockets only when the EOG option is used (RFQ 3.1).</t>
+          <t>1x6 socket: AVDD, AVSS, BIASIN, AGND_REF and a second rail pair</t>
         </is>
       </c>
       <c r="I35" s="4" t="n"/>
@@ -4501,22 +4501,22 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>J23</t>
+          <t>J24</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ADS1299 module #1 analogue rails</t>
+          <t>Charge input from the panel USB-C</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x06_P2.54mm_Vertical</t>
+          <t>JST_PH_B2B-PH-K_1x02_P2.00mm_Vertical</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-106-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>JST B2B-PH-K-S(LF)(SN)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>1x6 socket: AVDD, AVSS, BIASIN, AGND_REF and a second rail pair</t>
+          <t>charge-only USB-C receptacle pigtail; no data conductor enters here</t>
         </is>
       </c>
       <c r="I36" s="4" t="n"/>
@@ -4540,22 +4540,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>J24</t>
+          <t>J25</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Charge input from the panel USB-C</t>
+          <t>Buck-boost module, TPS63020 class</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>JST_PH_B2B-PH-K_1x02_P2.00mm_Vertical</t>
+          <t>PinSocket_1x06_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>JST B2B-PH-K-S(LF)(SN)</t>
+          <t>Samtec SSW-106-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>charge-only USB-C receptacle pigtail; no data conductor enters here</t>
+          <t>1x6: VSYS to a regulated 5.0 V rail for the DevKit and both ADS1299 modules</t>
         </is>
       </c>
       <c r="I37" s="4" t="n"/>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>J25</t>
+          <t>J26</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Buck-boost module, TPS63020 class</t>
+          <t>Debug / programming header</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>1x6: VSYS to a regulated 5.0 V rail for the DevKit and both ADS1299 modules</t>
+          <t>1x6: 3V3, GND, UART0 TX and RX, EN and NC_GPIO0 -- console and recovery flashing. Way 6 is the spare NC_GPIO0, not GPIO0: GPIO0 is committed to LED_SR_LATCH.</t>
         </is>
       </c>
       <c r="I38" s="4" t="n"/>
@@ -4618,22 +4618,22 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>J26</t>
+          <t>J27</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Debug / programming header</t>
+          <t>Headphone jack pigtail</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x06_P2.54mm_Vertical</t>
+          <t>PinSocket_1x04_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-106-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-104-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>1x6: 3V3, GND, UART0 TX and RX, EN and NC_GPIO0 -- console and recovery flashing. Way 6 is the spare NC_GPIO0, not GPIO0: GPIO0 is committed to LED_SR_LATCH.</t>
+          <t>1x4: to the panel 3.5 mm headphone jack</t>
         </is>
       </c>
       <c r="I39" s="4" t="n"/>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>J27</t>
+          <t>J28</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Headphone jack pigtail</t>
+          <t>Room microphone module</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>1x4: to the panel 3.5 mm headphone jack</t>
+          <t>1x4: outward-facing room microphone module with hardware mute</t>
         </is>
       </c>
       <c r="I40" s="4" t="n"/>
@@ -4696,22 +4696,22 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>J28</t>
+          <t>J29</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Room microphone module</t>
+          <t>ADS1299 module #2 analogue rails</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x04_P2.54mm_Vertical</t>
+          <t>PinSocket_1x06_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-104-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-106-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>1x4: outward-facing room microphone module with hardware mute</t>
+          <t>1x6 socket: AVDD2, AVSS2, BIASIN, AGND_REF and a second rail pair</t>
         </is>
       </c>
       <c r="I41" s="4" t="n"/>
@@ -4735,22 +4735,22 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>J29</t>
+          <t>J30</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>ADS1299 module #2 analogue rails</t>
+          <t>Helmet harness -- contact lights (10-way)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x06_P2.54mm_Vertical</t>
+          <t>PinSocket_1x10_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-106-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Samtec SSW-110-01-G-S or equivalent 2.54 mm socket strip</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>1x6 socket: AVDD2, AVSS2, BIASIN, AGND_REF and a second rail pair</t>
+          <t>1x10 socket: eight contact-light lines, the light common and its return. This is the second helmet cable; it carries no electrode signal.</t>
         </is>
       </c>
       <c r="I42" s="4" t="n"/>
@@ -4774,22 +4774,22 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>J30</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Helmet harness -- contact lights (10-way)</t>
+          <t>600R at 100 MHz, 500 mA</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_1x10_P2.54mm_Vertical</t>
+          <t>L_0603_1608Metric</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-110-01-G-S or equivalent 2.54 mm socket strip</t>
+          <t>Murata BLM18AG601SN1D</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>1x10 socket: eight contact-light lines, the light common and its return. This is the second helmet cable; it carries no electrode signal.</t>
+          <t>ferrite between DVDD3V3 and the isolator device-side supply</t>
         </is>
       </c>
       <c r="I43" s="4" t="n"/>
@@ -4809,26 +4809,26 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>R1 R2 R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>600R at 100 MHz, 1.5 A</t>
+          <t>68k 0.1% 25ppm</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>L_0603_1608Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Murata BLM18PG601SN1D</t>
+          <t>Vishay TNPW060368K0BEEA</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>ferrite between DVDD3V3 and the isolator device-side supply</t>
+          <t>series protection resistor, Fz scalp</t>
         </is>
       </c>
       <c r="I44" s="4" t="n"/>
@@ -4848,16 +4848,16 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>R1 R2 R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16</t>
+          <t>R20 R21 R23 R24 R40 R41 R43 R44 R60 R61 R63 R64</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>47k 0.1% 25ppm</t>
+          <t>10k 0.1%</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Vishay TNPW060347K0BEEA</t>
+          <t>Vishay TNPW060310K0BEEA</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>series protection resistor, Fz scalp</t>
+          <t>rectifier input resistor, envelope channel 1</t>
         </is>
       </c>
       <c r="I45" s="4" t="n"/>
@@ -4887,16 +4887,16 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>R20 R21 R23 R24 R40 R41 R43 R44 R60 R61 R63 R64</t>
+          <t>R22 R42 R62</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>10k 0.1%</t>
+          <t>4k99 0.1%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Vishay TNPW060310K0BEEA</t>
+          <t>Vishay TNPW06034K99BEEA</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>rectifier input resistor, envelope channel 1</t>
+          <t>half-wave summing resistor (R/2) into the absolute-value stage, channel 1</t>
         </is>
       </c>
       <c r="I46" s="4" t="n"/>
@@ -4926,16 +4926,16 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>R22 R42 R62</t>
+          <t>R25 R26 R45 R46 R65 R66</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>4k99 0.1%</t>
+          <t>215k 0.1%</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Vishay TNPW06034K99BEEA</t>
+          <t>Vishay TNPW0603215KBEEA</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>half-wave summing resistor (R/2) into the absolute-value stage, channel 1</t>
+          <t>Sallen-Key R1, channel 1</t>
         </is>
       </c>
       <c r="I47" s="4" t="n"/>
@@ -4965,11 +4965,11 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>R25 R26 R27 R45 R46 R47 R65 R66 R67</t>
+          <t>R27 R47 R67</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Sallen-Key R1, channel 1</t>
+          <t>output divider, top, channel 1</t>
         </is>
       </c>
       <c r="I48" s="4" t="n"/>
@@ -5408,12 +5408,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>SW_PUSH_6mm_H5mm</t>
+          <t>SW_PUSH_6mm_H7.3mm</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Omron B3F-4055</t>
+          <t>Omron B3F-1052</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>SW_PUSH_6mm_H5mm</t>
+          <t>SW_PUSH_6mm_H7.3mm</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Omron B3F-4055</t>
+          <t>Omron B3F-1052</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -5486,12 +5486,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>SW_PUSH_6mm_H5mm</t>
+          <t>SW_PUSH_6mm_H7.3mm</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Omron B3F-4055</t>
+          <t>Omron B3F-1052</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -6222,17 +6222,17 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>OPA4376AID</t>
+          <t>OPA4376AIPW</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>SOIC-14_3.9x8.7mm_P1.27mm</t>
+          <t>TSSOP-14_4.4x5mm_P0.65mm</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>TI OPA4376AIDR</t>
+          <t>TI OPA4376AIPWR</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -6291,7 +6291,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>GENERATED from package_v2.2/tools/design.py by tools/emit_workbooks.py. Do not edit by hand: edit design.py and regenerate, so this sheet and the board can never disagree.</t>
+          <t>GENERATED from package_v2.4/tools/design.py by tools/emit_workbooks.py. Do not edit by hand: edit design.py and regenerate, so this sheet and the board can never disagree.</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Revision C, 1 September 2026. Companion to RFQ-EEG-001 Rev E and DSN-EEG-003 Rev C.</t>
+          <t>Revision C, 1 September 2026. Companion to RFQ-EEG-001 Rev E and DSN-EEG-003 Rev D.</t>
         </is>
       </c>
     </row>
